--- a/docs/forms/D1_Data_Capture_KoBo.xlsx
+++ b/docs/forms/D1_Data_Capture_KoBo.xlsx
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
